--- a/artfynd/A 59947-2025 artfynd.xlsx
+++ b/artfynd/A 59947-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130486709</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59947-2025 artfynd.xlsx
+++ b/artfynd/A 59947-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130486709</v>
       </c>
       <c r="B2" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59947-2025 artfynd.xlsx
+++ b/artfynd/A 59947-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130486709</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59947-2025 artfynd.xlsx
+++ b/artfynd/A 59947-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130486709</v>
       </c>
       <c r="B2" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59947-2025 artfynd.xlsx
+++ b/artfynd/A 59947-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130486709</v>
       </c>
       <c r="B2" t="n">
-        <v>57067</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
